--- a/public/file/Done Payment Update Status Template.xlsx
+++ b/public/file/Done Payment Update Status Template.xlsx
@@ -14,18 +14,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Payment ID</t>
   </si>
   <si>
     <t>Status</t>
   </si>
+  <si>
+    <t>Company Bank ID</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -362,18 +365,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>

--- a/public/file/Done Payment Update Status Template.xlsx
+++ b/public/file/Done Payment Update Status Template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
